--- a/StructureDefinition-ncpi-sample.xlsx
+++ b/StructureDefinition-ncpi-sample.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T23:53:55+00:00</t>
+    <t>2025-12-03T18:37:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -352,7 +352,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -557,7 +557,7 @@
     <t>Specimen.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group|Device|Substance|Location)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1|Device|4.0.1|Substance|4.0.1|Location|4.0.1)
 </t>
   </si>
   <si>
@@ -601,7 +601,7 @@
     <t>Specimen.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -620,7 +620,7 @@
     <t>Specimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -755,7 +755,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -808,7 +808,7 @@
     <t>Specimen.collection.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -836,7 +836,7 @@
     <t>The  technique that is used to perform the procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -860,7 +860,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>.targetSiteCode</t>
@@ -948,13 +948,13 @@
     <t>Type indicating the technique used to process the specimen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance)
+    <t xml:space="preserve">Reference(Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -1069,7 +1069,7 @@
     <t>Type of specimen container.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
   </si>
   <si>
     <t>SPM-27</t>
@@ -1109,7 +1109,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>Additive associated with container</t>
@@ -1497,7 +1497,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="49.63671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.75" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="52.27734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-ncpi-sample.xlsx
+++ b/StructureDefinition-ncpi-sample.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T18:37:31+00:00</t>
+    <t>2025-12-03T22:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>NCPI FHIR Working Group (http://example.org/example-publisher, ncpi-fhir-ig@googlegroups.com)</t>
+    <t>NCPI FHIR Working Group (https://www.ncpi-acc.org/about/working-groups, ncpi-fhir-ig@googlegroups.com)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-ncpi-sample.xlsx
+++ b/StructureDefinition-ncpi-sample.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T22:26:51+00:00</t>
+    <t>2026-01-13T18:03:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-sample.xlsx
+++ b/StructureDefinition-ncpi-sample.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-13T18:03:13+00:00</t>
+    <t>2026-02-06T18:07:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ncpi-sample.xlsx
+++ b/StructureDefinition-ncpi-sample.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-06T18:07:39+00:00</t>
+    <t>2026-03-09T20:11:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
